--- a/backend/data/financials_by_company/002489.SZ.xlsx
+++ b/backend/data/financials_by_company/002489.SZ.xlsx
@@ -697,666 +697,666 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>18042916.117612</v>
+        <v>-22309350.378205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.108957</v>
+        <v>0.133804</v>
       </c>
       <c r="D2" t="n">
-        <v>541228495.3099999</v>
+        <v>467694159.24</v>
       </c>
       <c r="E2" t="n">
-        <v>165596417.16</v>
+        <v>-166731753.68</v>
       </c>
       <c r="F2" t="n">
-        <v>165596417.16</v>
+        <v>-166731753.68</v>
       </c>
       <c r="G2" t="n">
-        <v>462044337.79</v>
+        <v>125182002.36</v>
       </c>
       <c r="H2" t="n">
-        <v>150664107.08</v>
+        <v>133422882.9</v>
       </c>
       <c r="I2" t="n">
-        <v>4504866770.99</v>
+        <v>6998874885.29</v>
       </c>
       <c r="J2" t="n">
-        <v>706824912.47</v>
+        <v>300962405.56</v>
       </c>
       <c r="K2" t="n">
-        <v>556160805.39</v>
+        <v>167539522.66</v>
       </c>
       <c r="L2" t="n">
-        <v>15871770.6</v>
+        <v>-4561488.96</v>
       </c>
       <c r="M2" t="n">
-        <v>26063920.83</v>
+        <v>26121719.78</v>
       </c>
       <c r="N2" t="n">
-        <v>44617977.8</v>
+        <v>25074917.15</v>
       </c>
       <c r="O2" t="n">
-        <v>314490836.747612</v>
+        <v>269604405.661795</v>
       </c>
       <c r="P2" t="n">
-        <v>462044337.79</v>
+        <v>125182002.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>5415642127.81</v>
+        <v>7957954368.27</v>
       </c>
       <c r="R2" t="n">
-        <v>26908714.9</v>
+        <v>45529579</v>
       </c>
       <c r="S2" t="n">
-        <v>534551359.44</v>
+        <v>147832521.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2200211132</v>
+        <v>2086366706</v>
       </c>
       <c r="U2" t="n">
-        <v>2200211132</v>
+        <v>2086366706</v>
       </c>
       <c r="V2" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="X2" t="n">
-        <v>462044337.79</v>
+        <v>125182002.36</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>462044337.79</v>
+        <v>125182002.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>-10294693.15</v>
+        <v>2686445.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>472339030.94</v>
+        <v>122495556.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>472339030.94</v>
+        <v>122495556.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>57757853.62</v>
+        <v>18922246.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>530096884.56</v>
+        <v>141417802.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4454474.88</v>
+        <v>-7642415.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>72365696.18000001</v>
+        <v>-174455280.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>-174017924.97</v>
+        <v>-19362.27</v>
       </c>
       <c r="AI2" t="n">
-        <v>44165469.31</v>
+        <v>102097722.87</v>
       </c>
       <c r="AJ2" t="n">
-        <v>57486759.48</v>
+        <v>72376919.45999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>15871770.6</v>
+        <v>-4561488.96</v>
       </c>
       <c r="AL2" t="n">
-        <v>2682286.37</v>
+        <v>3514686.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>26063920.83</v>
+        <v>26121719.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>44617977.8</v>
+        <v>25074917.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>259856936.51</v>
+        <v>192855310.29</v>
       </c>
       <c r="AP2" t="n">
-        <v>910775356.8200001</v>
+        <v>959079482.98</v>
       </c>
       <c r="AQ2" t="n">
-        <v>64343749.05</v>
+        <v>64086859.81</v>
       </c>
       <c r="AR2" t="n">
-        <v>42147290.17</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>34516765.28</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15545449.1</v>
+      </c>
       <c r="AT2" t="n">
-        <v>42147290.17</v>
+        <v>18971316.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>145949938.67</v>
+        <v>222586885.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>305857896.1</v>
+        <v>344294288.68</v>
       </c>
       <c r="AW2" t="n">
-        <v>173015962.21</v>
+        <v>214815934.68</v>
       </c>
       <c r="AX2" t="n">
-        <v>132841933.89</v>
+        <v>129478354</v>
       </c>
       <c r="AY2" t="n">
-        <v>26908714.9</v>
+        <v>45529579</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1170632293.33</v>
+        <v>1151934793.27</v>
       </c>
       <c r="BA2" t="n">
-        <v>4504866770.99</v>
+        <v>6998874885.29</v>
       </c>
       <c r="BB2" t="n">
-        <v>5675499064.32</v>
+        <v>8150809678.56</v>
       </c>
       <c r="BC2" t="n">
-        <v>5675499064.32</v>
+        <v>8150809678.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-9576803.67</v>
+        <v>-33087754.028988</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.218297</v>
       </c>
       <c r="D3" t="n">
-        <v>339620089.11</v>
+        <v>548124772.39</v>
       </c>
       <c r="E3" t="n">
-        <v>-38307214.68</v>
+        <v>-151572398.73</v>
       </c>
       <c r="F3" t="n">
-        <v>-38307214.68</v>
+        <v>-151572398.73</v>
       </c>
       <c r="G3" t="n">
-        <v>50870804.1</v>
+        <v>216286347.73</v>
       </c>
       <c r="H3" t="n">
-        <v>155608216.05</v>
+        <v>161762427.33</v>
       </c>
       <c r="I3" t="n">
-        <v>3717903628.27</v>
+        <v>6805333269.3</v>
       </c>
       <c r="J3" t="n">
-        <v>301312874.43</v>
+        <v>396552373.66</v>
       </c>
       <c r="K3" t="n">
-        <v>145704658.38</v>
+        <v>234789946.33</v>
       </c>
       <c r="L3" t="n">
-        <v>4700205.98</v>
+        <v>-5605489.07</v>
       </c>
       <c r="M3" t="n">
-        <v>52960218.09</v>
+        <v>29292318.67</v>
       </c>
       <c r="N3" t="n">
-        <v>59693691.65</v>
+        <v>26786466.8</v>
       </c>
       <c r="O3" t="n">
-        <v>79601215.11</v>
+        <v>334770992.431012</v>
       </c>
       <c r="P3" t="n">
-        <v>50870804.1</v>
+        <v>216286347.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>4649755868.17</v>
+        <v>7834004242.49</v>
       </c>
       <c r="R3" t="n">
-        <v>59038455.8</v>
+        <v>74841277.55</v>
       </c>
       <c r="S3" t="n">
-        <v>107868764.44</v>
+        <v>219304405.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2543540205</v>
+        <v>2162863477</v>
       </c>
       <c r="U3" t="n">
-        <v>2543540205</v>
+        <v>2162863477</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="X3" t="n">
-        <v>50870804.1</v>
+        <v>216286347.73</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>50870804.1</v>
+        <v>216286347.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>14712306.45</v>
+        <v>55648173.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>36158497.65</v>
+        <v>160638174.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>36158497.65</v>
+        <v>160638174.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>56585942.64</v>
+        <v>44859453.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>92744440.29000001</v>
+        <v>205497627.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>-15124324.15</v>
+        <v>-18229040.29</v>
       </c>
       <c r="AG3" t="n">
-        <v>-43366425.21</v>
+        <v>-84950940.54000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>160894.33</v>
+        <v>-437166.68</v>
       </c>
       <c r="AI3" t="n">
-        <v>-42486333.39</v>
+        <v>-118426978.36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85691864.27</v>
+        <v>203815085.58</v>
       </c>
       <c r="AK3" t="n">
-        <v>4700205.98</v>
+        <v>-5605489.07</v>
       </c>
       <c r="AL3" t="n">
-        <v>2033267.58</v>
+        <v>3099637.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>52960218.09</v>
+        <v>29292318.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>59693691.65</v>
+        <v>26786466.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>187507650.7</v>
+        <v>385106405</v>
       </c>
       <c r="AP3" t="n">
-        <v>931852239.9</v>
+        <v>1028670973.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>35602832.24</v>
+        <v>55445331.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>40765563.43</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>30029713.38</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>13178265.05</v>
+      </c>
       <c r="AT3" t="n">
-        <v>40765563.43</v>
+        <v>16851448.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>166014728.08</v>
+        <v>177363025.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>338752394.72</v>
+        <v>422197076.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>208203343.4</v>
+        <v>271755691.73</v>
       </c>
       <c r="AX3" t="n">
-        <v>130549051.32</v>
+        <v>150441384.38</v>
       </c>
       <c r="AY3" t="n">
-        <v>59038455.8</v>
+        <v>74841277.55</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1119359890.6</v>
+        <v>1413777378.19</v>
       </c>
       <c r="BA3" t="n">
-        <v>3717903628.27</v>
+        <v>6805333269.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>4837263518.87</v>
+        <v>8219110647.49</v>
       </c>
       <c r="BC3" t="n">
-        <v>4837263518.87</v>
+        <v>8219110647.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-33087754.028988</v>
+        <v>-9576803.67</v>
       </c>
       <c r="C4" t="n">
-        <v>0.218297</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>548124772.39</v>
+        <v>339620089.11</v>
       </c>
       <c r="E4" t="n">
-        <v>-151572398.73</v>
+        <v>-38307214.68</v>
       </c>
       <c r="F4" t="n">
-        <v>-151572398.73</v>
+        <v>-38307214.68</v>
       </c>
       <c r="G4" t="n">
-        <v>216286347.73</v>
+        <v>50870804.1</v>
       </c>
       <c r="H4" t="n">
-        <v>161762427.33</v>
+        <v>155608216.05</v>
       </c>
       <c r="I4" t="n">
-        <v>6805333269.3</v>
+        <v>3717903628.27</v>
       </c>
       <c r="J4" t="n">
-        <v>396552373.66</v>
+        <v>301312874.43</v>
       </c>
       <c r="K4" t="n">
-        <v>234789946.33</v>
+        <v>145704658.38</v>
       </c>
       <c r="L4" t="n">
-        <v>-5605489.07</v>
+        <v>4700205.98</v>
       </c>
       <c r="M4" t="n">
-        <v>29292318.67</v>
+        <v>52960218.09</v>
       </c>
       <c r="N4" t="n">
-        <v>26786466.8</v>
+        <v>59693691.65</v>
       </c>
       <c r="O4" t="n">
-        <v>334770992.431012</v>
+        <v>79601215.11</v>
       </c>
       <c r="P4" t="n">
-        <v>216286347.73</v>
+        <v>50870804.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>7834004242.49</v>
+        <v>4649755868.17</v>
       </c>
       <c r="R4" t="n">
-        <v>74841277.55</v>
+        <v>59038455.8</v>
       </c>
       <c r="S4" t="n">
-        <v>219304405.85</v>
+        <v>107868764.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2162863477</v>
+        <v>2543540205</v>
       </c>
       <c r="U4" t="n">
-        <v>2162863477</v>
+        <v>2543540205</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="X4" t="n">
-        <v>216286347.73</v>
+        <v>50870804.1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>216286347.73</v>
+        <v>50870804.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>55648173.47</v>
+        <v>14712306.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>160638174.26</v>
+        <v>36158497.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>160638174.26</v>
+        <v>36158497.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>44859453.4</v>
+        <v>56585942.64</v>
       </c>
       <c r="AE4" t="n">
-        <v>205497627.66</v>
+        <v>92744440.29000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>-18229040.29</v>
+        <v>-15124324.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>-84950940.54000001</v>
+        <v>-43366425.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>-437166.68</v>
+        <v>160894.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>-118426978.36</v>
+        <v>-42486333.39</v>
       </c>
       <c r="AJ4" t="n">
-        <v>203815085.58</v>
+        <v>85691864.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5605489.07</v>
+        <v>4700205.98</v>
       </c>
       <c r="AL4" t="n">
-        <v>3099637.2</v>
+        <v>2033267.58</v>
       </c>
       <c r="AM4" t="n">
-        <v>29292318.67</v>
+        <v>52960218.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>26786466.8</v>
+        <v>59693691.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>385106405</v>
+        <v>187507650.7</v>
       </c>
       <c r="AP4" t="n">
-        <v>1028670973.19</v>
+        <v>931852239.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>55445331.6</v>
+        <v>35602832.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>30029713.38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>13178265.05</v>
-      </c>
+        <v>40765563.43</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>16851448.33</v>
+        <v>40765563.43</v>
       </c>
       <c r="AU4" t="n">
-        <v>177363025.45</v>
+        <v>166014728.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>422197076.11</v>
+        <v>338752394.72</v>
       </c>
       <c r="AW4" t="n">
-        <v>271755691.73</v>
+        <v>208203343.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>150441384.38</v>
+        <v>130549051.32</v>
       </c>
       <c r="AY4" t="n">
-        <v>74841277.55</v>
+        <v>59038455.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1413777378.19</v>
+        <v>1119359890.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6805333269.3</v>
+        <v>3717903628.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>8219110647.49</v>
+        <v>4837263518.87</v>
       </c>
       <c r="BC4" t="n">
-        <v>8219110647.49</v>
+        <v>4837263518.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-22309350.378205</v>
+        <v>18042916.117612</v>
       </c>
       <c r="C5" t="n">
-        <v>0.133804</v>
+        <v>0.108957</v>
       </c>
       <c r="D5" t="n">
-        <v>467694159.24</v>
+        <v>541228495.3099999</v>
       </c>
       <c r="E5" t="n">
-        <v>-166731753.68</v>
+        <v>165596417.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-166731753.68</v>
+        <v>165596417.16</v>
       </c>
       <c r="G5" t="n">
-        <v>125182002.36</v>
+        <v>462044337.79</v>
       </c>
       <c r="H5" t="n">
-        <v>133422882.9</v>
+        <v>150664107.08</v>
       </c>
       <c r="I5" t="n">
-        <v>6998874885.29</v>
+        <v>4504866770.99</v>
       </c>
       <c r="J5" t="n">
-        <v>300962405.56</v>
+        <v>706824912.47</v>
       </c>
       <c r="K5" t="n">
-        <v>167539522.66</v>
+        <v>556160805.39</v>
       </c>
       <c r="L5" t="n">
-        <v>-4561488.96</v>
+        <v>15871770.6</v>
       </c>
       <c r="M5" t="n">
-        <v>26121719.78</v>
+        <v>26063920.83</v>
       </c>
       <c r="N5" t="n">
-        <v>25074917.15</v>
+        <v>44617977.8</v>
       </c>
       <c r="O5" t="n">
-        <v>269604405.661795</v>
+        <v>314490836.747612</v>
       </c>
       <c r="P5" t="n">
-        <v>125182002.36</v>
+        <v>462044337.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>7957954368.27</v>
+        <v>5415642127.81</v>
       </c>
       <c r="R5" t="n">
-        <v>45529579</v>
+        <v>26908714.9</v>
       </c>
       <c r="S5" t="n">
-        <v>147832521.95</v>
+        <v>534551359.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2086366706</v>
+        <v>2200211132</v>
       </c>
       <c r="U5" t="n">
-        <v>2086366706</v>
+        <v>2200211132</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="X5" t="n">
-        <v>125182002.36</v>
+        <v>462044337.79</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>125182002.36</v>
+        <v>462044337.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>2686445.81</v>
+        <v>-10294693.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>122495556.55</v>
+        <v>472339030.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>122495556.55</v>
+        <v>472339030.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>18922246.33</v>
+        <v>57757853.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>141417802.88</v>
+        <v>530096884.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7642415.66</v>
+        <v>-4454474.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>-174455280.06</v>
+        <v>72365696.18000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>-19362.27</v>
+        <v>-174017924.97</v>
       </c>
       <c r="AI5" t="n">
-        <v>102097722.87</v>
+        <v>44165469.31</v>
       </c>
       <c r="AJ5" t="n">
-        <v>72376919.45999999</v>
+        <v>57486759.48</v>
       </c>
       <c r="AK5" t="n">
-        <v>-4561488.96</v>
+        <v>15871770.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>3514686.33</v>
+        <v>2682286.37</v>
       </c>
       <c r="AM5" t="n">
-        <v>26121719.78</v>
+        <v>26063920.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>25074917.15</v>
+        <v>44617977.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>192855310.29</v>
+        <v>259856936.51</v>
       </c>
       <c r="AP5" t="n">
-        <v>959079482.98</v>
+        <v>910775356.8200001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>64086859.81</v>
+        <v>64343749.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>34516765.28</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15545449.1</v>
-      </c>
+        <v>42147290.17</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>18971316.18</v>
+        <v>42147290.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>222586885.27</v>
+        <v>145949938.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>344294288.68</v>
+        <v>305857896.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>214815934.68</v>
+        <v>173015962.21</v>
       </c>
       <c r="AX5" t="n">
-        <v>129478354</v>
+        <v>132841933.89</v>
       </c>
       <c r="AY5" t="n">
-        <v>45529579</v>
+        <v>26908714.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1151934793.27</v>
+        <v>1170632293.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>6998874885.29</v>
+        <v>4504866770.99</v>
       </c>
       <c r="BB5" t="n">
-        <v>8150809678.56</v>
+        <v>5675499064.32</v>
       </c>
       <c r="BC5" t="n">
-        <v>8150809678.56</v>
+        <v>5675499064.32</v>
       </c>
     </row>
   </sheetData>
@@ -1737,302 +1737,414 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2175736503</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2175736503</v>
+      </c>
+      <c r="D2" t="n">
+        <v>154584021.47</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1808982988.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3254258392.69</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5273736514.21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1292121143.17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3254258392.69</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21054899.32</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3511577862.63</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>213248111.56</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>3511577862.63</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3588855727.99</v>
+      </c>
+      <c r="O2" t="n">
+        <v>77277865.36</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3511577862.63</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>28648921.32</v>
+      </c>
+      <c r="R2" t="n">
+        <v>809705968.65</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2175736503</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2175736503</v>
+      </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>5873544673.78</v>
+      </c>
+      <c r="X2" t="n">
+        <v>45190387.77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1800650</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22334838.45</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>21054899.32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>21054899.32</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5828354286.01</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3450110.89</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1787928089.08</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1762158651.58</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4022691043.51</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>199036747</v>
+      </c>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>118806370.08</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3704847926.43</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>9462400401.77</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2341924972.59</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>32692094.13</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>43001060.98</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>803298162.63</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>803298162.63</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>148966485.15</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>176710324.31</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>257319469.94</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>257319469.94</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>588073659.03</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>466699096.41</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>214941780.5</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>879937375.45</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-909587903.38</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1789525278.83</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>24832694.79</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>582375575.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>31305891.83</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1151011117.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7120475429.18</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>314757404.02</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>170824901.06</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2362918437.9</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>12714067.73</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>2225688061.13</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-250455923.25</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>2476143984.38</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>2033572557.34</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>425997927.23</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1607574630.11</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>465297998.89</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1142276631.22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2169016313</v>
+        <v>2175736503</v>
       </c>
       <c r="C3" t="n">
-        <v>2169016313</v>
-      </c>
-      <c r="D3" t="n">
-        <v>256807720.88</v>
-      </c>
+        <v>2175736503</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1167321616.89</v>
+        <v>2109931232.09</v>
       </c>
       <c r="F3" t="n">
-        <v>3728566952.08</v>
+        <v>3287207503.95</v>
       </c>
       <c r="G3" t="n">
-        <v>5117090913.39</v>
+        <v>4882820596.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1629688756.27</v>
+        <v>1288372970.45</v>
       </c>
       <c r="I3" t="n">
-        <v>3728566952.08</v>
+        <v>3287207503.95</v>
       </c>
       <c r="J3" t="n">
-        <v>104096800.89</v>
+        <v>67751492.40000001</v>
       </c>
       <c r="K3" t="n">
-        <v>4090004038.39</v>
+        <v>3533390199.17</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>4090004038.39</v>
+        <v>3533390199.17</v>
       </c>
       <c r="N3" t="n">
-        <v>4136798215.95</v>
+        <v>3560219126.24</v>
       </c>
       <c r="O3" t="n">
-        <v>46794177.56</v>
+        <v>26828927.07</v>
       </c>
       <c r="P3" t="n">
-        <v>4090004038.39</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>3533390199.17</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>28648921.32</v>
+      </c>
       <c r="R3" t="n">
-        <v>1290739854.74</v>
+        <v>916135102.28</v>
       </c>
       <c r="S3" t="n">
-        <v>213248111.56</v>
+        <v>226844376.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2169016313</v>
+        <v>2175736503</v>
       </c>
       <c r="U3" t="n">
-        <v>2169016313</v>
+        <v>2175736503</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>3856074015.34</v>
+        <v>4787825817.17</v>
       </c>
       <c r="X3" t="n">
-        <v>121373895.84</v>
+        <v>73630426.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>4722916.41</v>
+        <v>1501640</v>
       </c>
       <c r="Z3" t="n">
-        <v>12554178.54</v>
+        <v>4377293.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>104096800.89</v>
+        <v>67751492.40000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>104096800.89</v>
+        <v>67751492.40000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>3734700119.5</v>
+        <v>4714195391.03</v>
       </c>
       <c r="AD3" t="n">
-        <v>3129210.98</v>
+        <v>139828696.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1063224816</v>
+        <v>2042179739.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>1027086875</v>
+        <v>1349430397.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>2659263260.46</v>
+        <v>2519497842.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>223117172.56</v>
+        <v>192368706.81</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>48437261.55</v>
+        <v>96723314.44</v>
       </c>
       <c r="AK3" t="n">
-        <v>2387708826.35</v>
+        <v>2230405821.19</v>
       </c>
       <c r="AL3" t="n">
-        <v>7992872231.29</v>
+        <v>8348044943.41</v>
       </c>
       <c r="AM3" t="n">
-        <v>2628483355.52</v>
+        <v>2345476581.93</v>
       </c>
       <c r="AN3" t="n">
-        <v>377941480.92</v>
+        <v>20884955.76</v>
       </c>
       <c r="AO3" t="n">
-        <v>46082390.7</v>
+        <v>35558671.09</v>
       </c>
       <c r="AP3" t="n">
-        <v>29336137.59</v>
+        <v>61476898.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>649397470.25</v>
+        <v>735848021.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>649397470.25</v>
+        <v>735848021.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>139923439.83</v>
+        <v>148624833.15</v>
       </c>
       <c r="AT3" t="n">
-        <v>143396845.67</v>
+        <v>163934226.61</v>
       </c>
       <c r="AU3" t="n">
-        <v>361437086.31</v>
+        <v>246182695.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>354024684.39</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7412401.92</v>
-      </c>
+        <v>246182695.22</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>880968504.25</v>
+        <v>932966280.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1052762351.05</v>
+        <v>-970878138.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1933730855.3</v>
+        <v>1903844418.48</v>
       </c>
       <c r="BA3" t="n">
-        <v>16183373.48</v>
+        <v>41907515.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>692897107.3</v>
+        <v>658714593.62</v>
       </c>
       <c r="BC3" t="n">
-        <v>32978137.18</v>
+        <v>32421788.68</v>
       </c>
       <c r="BD3" t="n">
-        <v>1191672237.34</v>
+        <v>1170800520.73</v>
       </c>
       <c r="BE3" t="n">
-        <v>5364388875.77</v>
+        <v>6002568361.48</v>
       </c>
       <c r="BF3" t="n">
-        <v>136349604.52</v>
+        <v>89772992.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>45443356.59</v>
+        <v>38405528.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>1525171275.81</v>
+        <v>1676316491.45</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>837114699.01</v>
+        <v>872851709.37</v>
       </c>
       <c r="BK3" t="n">
-        <v>488047236.59</v>
+        <v>529028293.69</v>
       </c>
       <c r="BL3" t="n">
-        <v>200009340.21</v>
+        <v>274436488.39</v>
       </c>
       <c r="BM3" t="n">
-        <v>87698388.31</v>
+        <v>20893584.48</v>
       </c>
       <c r="BN3" t="n">
-        <v>2122943457.87</v>
+        <v>2268821469.66</v>
       </c>
       <c r="BO3" t="n">
-        <v>-129108380.79</v>
+        <v>-133192213.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>2252051838.66</v>
+        <v>2402013683.41</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1446782792.67</v>
+        <v>1908358294.98</v>
       </c>
       <c r="BR3" t="n">
-        <v>676503638.55</v>
+        <v>411065233.81</v>
       </c>
       <c r="BS3" t="n">
-        <v>770279154.12</v>
+        <v>1497293061.17</v>
       </c>
       <c r="BT3" t="n">
-        <v>26068850.81</v>
+        <v>761675642.9400001</v>
       </c>
       <c r="BU3" t="n">
-        <v>744210303.3099999</v>
+        <v>735617418.23</v>
       </c>
     </row>
     <row r="4">
@@ -2254,415 +2366,303 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2175736503</v>
+        <v>2169016313</v>
       </c>
       <c r="C5" t="n">
-        <v>2175736503</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>2169016313</v>
+      </c>
+      <c r="D5" t="n">
+        <v>256807720.88</v>
+      </c>
       <c r="E5" t="n">
-        <v>2109931232.09</v>
+        <v>1167321616.89</v>
       </c>
       <c r="F5" t="n">
-        <v>3287207503.95</v>
+        <v>3728566952.08</v>
       </c>
       <c r="G5" t="n">
-        <v>4882820596.66</v>
+        <v>5117090913.39</v>
       </c>
       <c r="H5" t="n">
-        <v>1288372970.45</v>
+        <v>1629688756.27</v>
       </c>
       <c r="I5" t="n">
-        <v>3287207503.95</v>
+        <v>3728566952.08</v>
       </c>
       <c r="J5" t="n">
-        <v>67751492.40000001</v>
+        <v>104096800.89</v>
       </c>
       <c r="K5" t="n">
-        <v>3533390199.17</v>
+        <v>4090004038.39</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>3533390199.17</v>
+        <v>4090004038.39</v>
       </c>
       <c r="N5" t="n">
-        <v>3560219126.24</v>
+        <v>4136798215.95</v>
       </c>
       <c r="O5" t="n">
-        <v>26828927.07</v>
+        <v>46794177.56</v>
       </c>
       <c r="P5" t="n">
-        <v>3533390199.17</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>28648921.32</v>
-      </c>
+        <v>4090004038.39</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>916135102.28</v>
+        <v>1290739854.74</v>
       </c>
       <c r="S5" t="n">
-        <v>226844376.43</v>
+        <v>213248111.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2175736503</v>
+        <v>2169016313</v>
       </c>
       <c r="U5" t="n">
-        <v>2175736503</v>
+        <v>2169016313</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>4787825817.17</v>
+        <v>3856074015.34</v>
       </c>
       <c r="X5" t="n">
-        <v>73630426.14</v>
+        <v>121373895.84</v>
       </c>
       <c r="Y5" t="n">
-        <v>1501640</v>
+        <v>4722916.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>4377293.74</v>
+        <v>12554178.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>67751492.40000001</v>
+        <v>104096800.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>67751492.40000001</v>
+        <v>104096800.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>4714195391.03</v>
+        <v>3734700119.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>139828696.45</v>
+        <v>3129210.98</v>
       </c>
       <c r="AE5" t="n">
-        <v>2042179739.69</v>
+        <v>1063224816</v>
       </c>
       <c r="AF5" t="n">
-        <v>1349430397.49</v>
+        <v>1027086875</v>
       </c>
       <c r="AG5" t="n">
-        <v>2519497842.44</v>
+        <v>2659263260.46</v>
       </c>
       <c r="AH5" t="n">
-        <v>192368706.81</v>
+        <v>223117172.56</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>96723314.44</v>
+        <v>48437261.55</v>
       </c>
       <c r="AK5" t="n">
-        <v>2230405821.19</v>
+        <v>2387708826.35</v>
       </c>
       <c r="AL5" t="n">
-        <v>8348044943.41</v>
+        <v>7992872231.29</v>
       </c>
       <c r="AM5" t="n">
-        <v>2345476581.93</v>
+        <v>2628483355.52</v>
       </c>
       <c r="AN5" t="n">
-        <v>20884955.76</v>
+        <v>377941480.92</v>
       </c>
       <c r="AO5" t="n">
-        <v>35558671.09</v>
+        <v>46082390.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>61476898.55</v>
+        <v>29336137.59</v>
       </c>
       <c r="AQ5" t="n">
-        <v>735848021.45</v>
+        <v>649397470.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>735848021.45</v>
+        <v>649397470.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>148624833.15</v>
+        <v>139923439.83</v>
       </c>
       <c r="AT5" t="n">
-        <v>163934226.61</v>
+        <v>143396845.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>246182695.22</v>
+        <v>361437086.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>246182695.22</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>354024684.39</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7412401.92</v>
+      </c>
       <c r="AX5" t="n">
-        <v>932966280.1</v>
+        <v>880968504.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>-970878138.38</v>
+        <v>-1052762351.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1903844418.48</v>
+        <v>1933730855.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>41907515.45</v>
+        <v>16183373.48</v>
       </c>
       <c r="BB5" t="n">
-        <v>658714593.62</v>
+        <v>692897107.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>32421788.68</v>
+        <v>32978137.18</v>
       </c>
       <c r="BD5" t="n">
-        <v>1170800520.73</v>
+        <v>1191672237.34</v>
       </c>
       <c r="BE5" t="n">
-        <v>6002568361.48</v>
+        <v>5364388875.77</v>
       </c>
       <c r="BF5" t="n">
-        <v>89772992.5</v>
+        <v>136349604.52</v>
       </c>
       <c r="BG5" t="n">
-        <v>38405528.41</v>
+        <v>45443356.59</v>
       </c>
       <c r="BH5" t="n">
-        <v>1676316491.45</v>
+        <v>1525171275.81</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>872851709.37</v>
+        <v>837114699.01</v>
       </c>
       <c r="BK5" t="n">
-        <v>529028293.69</v>
+        <v>488047236.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>274436488.39</v>
+        <v>200009340.21</v>
       </c>
       <c r="BM5" t="n">
-        <v>20893584.48</v>
+        <v>87698388.31</v>
       </c>
       <c r="BN5" t="n">
-        <v>2268821469.66</v>
+        <v>2122943457.87</v>
       </c>
       <c r="BO5" t="n">
-        <v>-133192213.75</v>
+        <v>-129108380.79</v>
       </c>
       <c r="BP5" t="n">
-        <v>2402013683.41</v>
+        <v>2252051838.66</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1908358294.98</v>
+        <v>1446782792.67</v>
       </c>
       <c r="BR5" t="n">
-        <v>411065233.81</v>
+        <v>676503638.55</v>
       </c>
       <c r="BS5" t="n">
-        <v>1497293061.17</v>
+        <v>770279154.12</v>
       </c>
       <c r="BT5" t="n">
-        <v>761675642.9400001</v>
+        <v>26068850.81</v>
       </c>
       <c r="BU5" t="n">
-        <v>735617418.23</v>
+        <v>744210303.3099999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2175736503</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2175736503</v>
-      </c>
-      <c r="D6" t="n">
-        <v>154584021.47</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1808982988.4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3254258392.69</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5273736514.21</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1292121143.17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3254258392.69</v>
-      </c>
-      <c r="J6" t="n">
-        <v>21054899.32</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3511577862.63</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>3511577862.63</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3588855727.99</v>
-      </c>
-      <c r="O6" t="n">
-        <v>77277865.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3511577862.63</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>28648921.32</v>
-      </c>
-      <c r="R6" t="n">
-        <v>809705968.65</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>2175736503</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2175736503</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>213248111.56</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>5873544673.78</v>
-      </c>
-      <c r="X6" t="n">
-        <v>45190387.77</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1800650</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>22334838.45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>21054899.32</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>21054899.32</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5828354286.01</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3450110.89</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1787928089.08</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1762158651.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4022691043.51</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>199036747</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>118806370.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3704847926.43</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>9462400401.77</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2341924972.59</v>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>32692094.13</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>43001060.98</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>803298162.63</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>803298162.63</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>148966485.15</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>176710324.31</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>257319469.94</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>257319469.94</v>
-      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>879937375.45</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-909587903.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1789525278.83</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>24832694.79</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>582375575.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>31305891.83</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1151011117.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7120475429.18</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>314757404.02</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>170824901.06</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2362918437.9</v>
-      </c>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>12714067.73</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>2225688061.13</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-250455923.25</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>2476143984.38</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>2033572557.34</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>425997927.23</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1607574630.11</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>465297998.89</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1142276631.22</v>
-      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>588073659.03</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>466699096.41</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>214941780.5</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2917,574 +2917,574 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>96515483.7</v>
+        <v>-325748315.7</v>
       </c>
       <c r="C2" t="n">
-        <v>-2874762040</v>
+        <v>-1664287800.07</v>
       </c>
       <c r="D2" t="n">
-        <v>2801580100</v>
+        <v>2277224135.6</v>
       </c>
       <c r="E2" t="n">
-        <v>-146349462.83</v>
+        <v>-150054765.89</v>
       </c>
       <c r="F2" t="n">
-        <v>747300354.12</v>
+        <v>1140639091.91</v>
       </c>
       <c r="G2" t="n">
-        <v>973090112.74</v>
+        <v>768526479.3099999</v>
       </c>
       <c r="H2" t="n">
-        <v>931843.42</v>
+        <v>249837349.94</v>
       </c>
       <c r="I2" t="n">
-        <v>-226721602.04</v>
+        <v>122275262.66</v>
       </c>
       <c r="J2" t="n">
-        <v>-168656552.42</v>
+        <v>234682598.87</v>
       </c>
       <c r="K2" t="n">
-        <v>-51827533.05</v>
+        <v>-26825178.33</v>
       </c>
       <c r="L2" t="n">
-        <v>-43480779.37</v>
+        <v>-351428558.33</v>
       </c>
       <c r="M2" t="n">
-        <v>-73181940</v>
+        <v>612936335.53</v>
       </c>
       <c r="N2" t="n">
-        <v>-73181940</v>
+        <v>612936335.53</v>
       </c>
       <c r="O2" t="n">
-        <v>-2874762040</v>
+        <v>-1664287800.07</v>
       </c>
       <c r="P2" t="n">
-        <v>2801580100</v>
+        <v>2277224135.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>-300929996.15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-368669383.72</v>
-      </c>
+        <v>63286213.6</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>30923520.99</v>
+        <v>211241476.32</v>
       </c>
       <c r="T2" t="n">
-        <v>358925823.33</v>
+        <v>856301629.8200001</v>
       </c>
       <c r="U2" t="n">
-        <v>-328002302.34</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-645060153.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-126498.34</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-126498.34</v>
+      </c>
       <c r="X2" t="n">
-        <v>36815866.58</v>
+        <v>-147828764.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>183165329.41</v>
+        <v>2226001.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>-146349462.83</v>
+        <v>-150054765.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>242864946.53</v>
+        <v>-175693549.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>-167171105.32</v>
+        <v>-508620831.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9688089.43</v>
+        <v>-24226946.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>933176386.95</v>
+        <v>1770998543.86</v>
       </c>
       <c r="AE2" t="n">
-        <v>-374897061.37</v>
+        <v>-757444813.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>-735138520.33</v>
+        <v>-1497947614.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>25347640</v>
+        <v>-132258575.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>150664107.08</v>
+        <v>133422882.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>13080377.22</v>
+        <v>15095789.03</v>
       </c>
       <c r="AJ2" t="n">
-        <v>137583729.86</v>
+        <v>118327093.87</v>
       </c>
       <c r="AK2" t="n">
-        <v>-171083409.09</v>
+        <v>37433975.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>-168883545.87</v>
+        <v>8450386.050000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>472339030.94</v>
+        <v>122495556.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>242864946.53</v>
+        <v>-175693549.81</v>
       </c>
       <c r="AO2" t="n">
-        <v>240367818.07</v>
+        <v>499881799.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>-5252067009.47</v>
+        <v>-8938470125.469999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-316750469.72</v>
+        <v>-898620480.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>-970985075.4299999</v>
+        <v>-997746117.59</v>
       </c>
       <c r="AS2" t="n">
-        <v>-3964331464.32</v>
+        <v>-7042103527.68</v>
       </c>
       <c r="AT2" t="n">
-        <v>5254564137.93</v>
+        <v>8262894775.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>153041508.59</v>
+        <v>291014541.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>5101522629.34</v>
+        <v>7971880234.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>715693585.8200001</v>
+        <v>102658642.4</v>
       </c>
       <c r="C3" t="n">
-        <v>-3429019876.78</v>
+        <v>-2124855700</v>
       </c>
       <c r="D3" t="n">
-        <v>3165888575</v>
+        <v>1725060800</v>
       </c>
       <c r="E3" t="n">
-        <v>-174736404.36</v>
+        <v>-133656370.3</v>
       </c>
       <c r="F3" t="n">
-        <v>973090112.74</v>
+        <v>738038066.88</v>
       </c>
       <c r="G3" t="n">
-        <v>738038066.88</v>
+        <v>1140639091.91</v>
       </c>
       <c r="H3" t="n">
-        <v>-159477701.95</v>
+        <v>100861462.33</v>
       </c>
       <c r="I3" t="n">
-        <v>394529747.81</v>
+        <v>-503462487.36</v>
       </c>
       <c r="J3" t="n">
-        <v>-373903022.85</v>
+        <v>-567219280.33</v>
       </c>
       <c r="K3" t="n">
-        <v>-23950913.23</v>
+        <v>-65812873.26</v>
       </c>
       <c r="L3" t="n">
-        <v>-86804130.06999999</v>
+        <v>-101003907.07</v>
       </c>
       <c r="M3" t="n">
-        <v>-263131301.78</v>
+        <v>-399794900</v>
       </c>
       <c r="N3" t="n">
-        <v>-263131301.78</v>
+        <v>-399794900</v>
       </c>
       <c r="O3" t="n">
-        <v>-3429019876.78</v>
+        <v>-2124855700</v>
       </c>
       <c r="P3" t="n">
-        <v>3165888575</v>
+        <v>1725060800</v>
       </c>
       <c r="Q3" t="n">
-        <v>-121997219.52</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-15382.14</v>
-      </c>
+        <v>-172558219.73</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>49913836.66</v>
+        <v>-41128474</v>
       </c>
       <c r="T3" t="n">
-        <v>433424658</v>
+        <v>95545220.76000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-383510821.34</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-4500000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-4500000</v>
-      </c>
+        <v>-136673694.76</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-167395674.04</v>
+        <v>-131429745.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>7340730.32</v>
+        <v>2226624.57</v>
       </c>
       <c r="Z3" t="n">
-        <v>-174736404.36</v>
+        <v>-133656370.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>890429990.1799999</v>
+        <v>236315012.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>540031735.12</v>
+        <v>-300468322.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>24337670.53</v>
+        <v>-1741124.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>-608623378.3099999</v>
+        <v>-1470510739.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>388297476.08</v>
+        <v>482786860.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>736019966.8200001</v>
+        <v>688996679.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>147857677.21</v>
+        <v>75256622.09999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>155608216.05</v>
+        <v>161762427.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>13081657.4</v>
+        <v>11723726.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>142526558.65</v>
+        <v>150038701.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>-37895918.44</v>
+        <v>43860047.31</v>
       </c>
       <c r="AL3" t="n">
-        <v>5464251.71</v>
+        <v>8751319.539999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>36158497.65</v>
+        <v>160638174.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>890429990.1799999</v>
+        <v>236315012.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>71091864.58</v>
+        <v>421910756.27</v>
       </c>
       <c r="AP3" t="n">
-        <v>-4765896380.23</v>
+        <v>-9157861481.639999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-542371784</v>
+        <v>-649166794.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>-836131414.88</v>
+        <v>-1024114828.79</v>
       </c>
       <c r="AS3" t="n">
-        <v>-3387393181.35</v>
+        <v>-7484579858.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>5585234505.83</v>
+        <v>8972265738.07</v>
       </c>
       <c r="AU3" t="n">
-        <v>206741645.24</v>
+        <v>540057126.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>5378492860.59</v>
+        <v>8432208611.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>102658642.4</v>
+        <v>715693585.8200001</v>
       </c>
       <c r="C4" t="n">
-        <v>-2124855700</v>
+        <v>-3429019876.78</v>
       </c>
       <c r="D4" t="n">
-        <v>1725060800</v>
+        <v>3165888575</v>
       </c>
       <c r="E4" t="n">
-        <v>-133656370.3</v>
+        <v>-174736404.36</v>
       </c>
       <c r="F4" t="n">
+        <v>973090112.74</v>
+      </c>
+      <c r="G4" t="n">
         <v>738038066.88</v>
       </c>
-      <c r="G4" t="n">
-        <v>1140639091.91</v>
-      </c>
       <c r="H4" t="n">
-        <v>100861462.33</v>
+        <v>-159477701.95</v>
       </c>
       <c r="I4" t="n">
-        <v>-503462487.36</v>
+        <v>394529747.81</v>
       </c>
       <c r="J4" t="n">
-        <v>-567219280.33</v>
+        <v>-373903022.85</v>
       </c>
       <c r="K4" t="n">
-        <v>-65812873.26</v>
+        <v>-23950913.23</v>
       </c>
       <c r="L4" t="n">
-        <v>-101003907.07</v>
+        <v>-86804130.06999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-399794900</v>
+        <v>-263131301.78</v>
       </c>
       <c r="N4" t="n">
-        <v>-399794900</v>
+        <v>-263131301.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-2124855700</v>
+        <v>-3429019876.78</v>
       </c>
       <c r="P4" t="n">
-        <v>1725060800</v>
+        <v>3165888575</v>
       </c>
       <c r="Q4" t="n">
-        <v>-172558219.73</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>-121997219.52</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-15382.14</v>
+      </c>
       <c r="S4" t="n">
-        <v>-41128474</v>
+        <v>49913836.66</v>
       </c>
       <c r="T4" t="n">
-        <v>95545220.76000001</v>
+        <v>433424658</v>
       </c>
       <c r="U4" t="n">
-        <v>-136673694.76</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-383510821.34</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-4500000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-4500000</v>
+      </c>
       <c r="X4" t="n">
-        <v>-131429745.73</v>
+        <v>-167395674.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>2226624.57</v>
+        <v>7340730.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>-133656370.3</v>
+        <v>-174736404.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>236315012.7</v>
+        <v>890429990.1799999</v>
       </c>
       <c r="AB4" t="n">
-        <v>-300468322.66</v>
+        <v>540031735.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1741124.26</v>
+        <v>24337670.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1470510739.17</v>
+        <v>-608623378.3099999</v>
       </c>
       <c r="AE4" t="n">
-        <v>482786860.87</v>
+        <v>388297476.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>688996679.9</v>
+        <v>736019966.8200001</v>
       </c>
       <c r="AG4" t="n">
-        <v>75256622.09999999</v>
+        <v>147857677.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>161762427.33</v>
+        <v>155608216.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>11723726.3</v>
+        <v>13081657.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150038701.03</v>
+        <v>142526558.65</v>
       </c>
       <c r="AK4" t="n">
-        <v>43860047.31</v>
+        <v>-37895918.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>8751319.539999999</v>
+        <v>5464251.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>160638174.26</v>
+        <v>36158497.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>236315012.7</v>
+        <v>890429990.1799999</v>
       </c>
       <c r="AO4" t="n">
-        <v>421910756.27</v>
+        <v>71091864.58</v>
       </c>
       <c r="AP4" t="n">
-        <v>-9157861481.639999</v>
+        <v>-4765896380.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-649166794.6</v>
+        <v>-542371784</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1024114828.79</v>
+        <v>-836131414.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>-7484579858.25</v>
+        <v>-3387393181.35</v>
       </c>
       <c r="AT4" t="n">
-        <v>8972265738.07</v>
+        <v>5585234505.83</v>
       </c>
       <c r="AU4" t="n">
-        <v>540057126.08</v>
+        <v>206741645.24</v>
       </c>
       <c r="AV4" t="n">
-        <v>8432208611.99</v>
+        <v>5378492860.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-325748315.7</v>
+        <v>96515483.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-1664287800.07</v>
+        <v>-2874762040</v>
       </c>
       <c r="D5" t="n">
-        <v>2277224135.6</v>
+        <v>2801580100</v>
       </c>
       <c r="E5" t="n">
-        <v>-150054765.89</v>
+        <v>-146349462.83</v>
       </c>
       <c r="F5" t="n">
-        <v>1140639091.91</v>
+        <v>747300354.12</v>
       </c>
       <c r="G5" t="n">
-        <v>768526479.3099999</v>
+        <v>973090112.74</v>
       </c>
       <c r="H5" t="n">
-        <v>249837349.94</v>
+        <v>931843.42</v>
       </c>
       <c r="I5" t="n">
-        <v>122275262.66</v>
+        <v>-226721602.04</v>
       </c>
       <c r="J5" t="n">
-        <v>234682598.87</v>
+        <v>-168656552.42</v>
       </c>
       <c r="K5" t="n">
-        <v>-26825178.33</v>
+        <v>-51827533.05</v>
       </c>
       <c r="L5" t="n">
-        <v>-351428558.33</v>
+        <v>-43480779.37</v>
       </c>
       <c r="M5" t="n">
-        <v>612936335.53</v>
+        <v>-73181940</v>
       </c>
       <c r="N5" t="n">
-        <v>612936335.53</v>
+        <v>-73181940</v>
       </c>
       <c r="O5" t="n">
-        <v>-1664287800.07</v>
+        <v>-2874762040</v>
       </c>
       <c r="P5" t="n">
-        <v>2277224135.6</v>
+        <v>2801580100</v>
       </c>
       <c r="Q5" t="n">
-        <v>63286213.6</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>-300929996.15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-368669383.72</v>
+      </c>
       <c r="S5" t="n">
-        <v>211241476.32</v>
+        <v>30923520.99</v>
       </c>
       <c r="T5" t="n">
-        <v>856301629.8200001</v>
+        <v>358925823.33</v>
       </c>
       <c r="U5" t="n">
-        <v>-645060153.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-126498.34</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-126498.34</v>
-      </c>
+        <v>-328002302.34</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-147828764.38</v>
+        <v>36815866.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>2226001.51</v>
+        <v>183165329.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>-150054765.89</v>
+        <v>-146349462.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>-175693549.81</v>
+        <v>242864946.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>-508620831.15</v>
+        <v>-167171105.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>-24226946.62</v>
+        <v>9688089.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1770998543.86</v>
+        <v>933176386.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>-757444813.73</v>
+        <v>-374897061.37</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1497947614.66</v>
+        <v>-735138520.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>-132258575.65</v>
+        <v>25347640</v>
       </c>
       <c r="AH5" t="n">
-        <v>133422882.9</v>
+        <v>150664107.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>15095789.03</v>
+        <v>13080377.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>118327093.87</v>
+        <v>137583729.86</v>
       </c>
       <c r="AK5" t="n">
-        <v>37433975.83</v>
+        <v>-171083409.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>8450386.050000001</v>
+        <v>-168883545.87</v>
       </c>
       <c r="AM5" t="n">
-        <v>122495556.55</v>
+        <v>472339030.94</v>
       </c>
       <c r="AN5" t="n">
-        <v>-175693549.81</v>
+        <v>242864946.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>499881799.76</v>
+        <v>240367818.07</v>
       </c>
       <c r="AP5" t="n">
-        <v>-8938470125.469999</v>
+        <v>-5252067009.47</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-898620480.2</v>
+        <v>-316750469.72</v>
       </c>
       <c r="AR5" t="n">
-        <v>-997746117.59</v>
+        <v>-970985075.4299999</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7042103527.68</v>
+        <v>-3964331464.32</v>
       </c>
       <c r="AT5" t="n">
-        <v>8262894775.9</v>
+        <v>5254564137.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>291014541.18</v>
+        <v>153041508.59</v>
       </c>
       <c r="AV5" t="n">
-        <v>7971880234.72</v>
+        <v>5101522629.34</v>
       </c>
     </row>
   </sheetData>
@@ -3498,7 +3498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL2"/>
+  <dimension ref="A1:EM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3659,555 +3659,560 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4299,34 +4304,34 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="T2" t="n">
-        <v>4.01</v>
+        <v>3.18</v>
       </c>
       <c r="U2" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>3.93</v>
+        <v>3.02</v>
       </c>
       <c r="W2" t="n">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="X2" t="n">
-        <v>4.01</v>
+        <v>3.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.93</v>
+        <v>3.02</v>
       </c>
       <c r="AA2" t="n">
         <v>0.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="AC2" t="n">
         <v>1780444800</v>
@@ -4338,382 +4343,385 @@
         <v>1.39</v>
       </c>
       <c r="AF2" t="n">
-        <v>34.272728</v>
+        <v>0.284</v>
       </c>
       <c r="AG2" t="n">
-        <v>57362766</v>
+        <v>26.727274</v>
       </c>
       <c r="AH2" t="n">
-        <v>57362766</v>
+        <v>43174804</v>
       </c>
       <c r="AI2" t="n">
-        <v>42146043</v>
+        <v>43174804</v>
       </c>
       <c r="AJ2" t="n">
-        <v>74735910</v>
+        <v>47347494</v>
       </c>
       <c r="AK2" t="n">
-        <v>74735910</v>
+        <v>44316343</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.77</v>
+        <v>44316343</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.78</v>
+        <v>2.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>8177191424</v>
+        <v>2.95</v>
       </c>
       <c r="AO2" t="n">
-        <v>8177191500</v>
+        <v>6376908288</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.16</v>
+        <v>6593809591</v>
       </c>
       <c r="AQ2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AR2" t="n">
         <v>4.21</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>14.851428</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>0.025094</v>
       </c>
-      <c r="AT2" t="n">
-        <v>1.4640967</v>
-      </c>
       <c r="AU2" t="n">
-        <v>3.5362</v>
+        <v>1.1417625</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.7267</v>
+        <v>3.5652</v>
       </c>
       <c r="AW2" t="n">
+        <v>3.70415</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0.06</v>
       </c>
-      <c r="AX2" t="n">
-        <v>0.015625</v>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" t="n">
+        <v>0.019736841</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="AZ2" t="b">
+      <c r="BA2" t="b">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
-        <v>7366377472</v>
-      </c>
       <c r="BB2" t="n">
+        <v>5395500544</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0.044499997</v>
       </c>
-      <c r="BC2" t="n">
-        <v>1027286800</v>
-      </c>
       <c r="BD2" t="n">
+        <v>1015316536</v>
+      </c>
+      <c r="BE2" t="n">
         <v>2169016313</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0.55062</v>
-      </c>
       <c r="BF2" t="n">
-        <v>0.02155</v>
+        <v>0.54644</v>
       </c>
       <c r="BG2" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="BH2" t="n">
         <v>2169016313</v>
       </c>
-      <c r="BH2" t="n">
-        <v>2.075</v>
-      </c>
       <c r="BI2" t="n">
-        <v>1.8168675</v>
+        <v>2.119</v>
       </c>
       <c r="BJ2" t="n">
+        <v>1.387447</v>
+      </c>
+      <c r="BK2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>-0.583</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>248549104</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>0.11</v>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>35:10</t>
         </is>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>1443052800</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1.319</v>
-      </c>
       <c r="BS2" t="n">
-        <v>30.354</v>
+        <v>0.966</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.01566577</v>
+        <v>23.089</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27697718</v>
+        <v>-0.14606744</v>
       </c>
       <c r="BV2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BW2" t="n">
         <v>0.06</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BX2" t="n">
         <v>1780444800</v>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BY2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BZ2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CA2" t="n">
+      <c r="CB2" t="n">
         <v>2285286912</v>
       </c>
-      <c r="CB2" t="n">
-        <v>1.032</v>
-      </c>
       <c r="CC2" t="n">
-        <v>242679120</v>
+        <v>1.054</v>
       </c>
       <c r="CD2" t="n">
+        <v>233684672</v>
+      </c>
+      <c r="CE2" t="n">
         <v>1294675584</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>1.306</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>1.553</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>5585144320</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>28.118</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>2.567</v>
       </c>
-      <c r="CJ2" t="n">
-        <v>0.01091</v>
-      </c>
       <c r="CK2" t="n">
+        <v>0.010240001</v>
+      </c>
+      <c r="CL2" t="n">
         <v>0.056560002</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>983623808</v>
       </c>
-      <c r="CM2" t="n">
-        <v>-347163488</v>
-      </c>
       <c r="CN2" t="n">
+        <v>-354109120</v>
+      </c>
+      <c r="CO2" t="n">
         <v>-61140864</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>-0.588</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>-0.029</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>0.17611</v>
       </c>
-      <c r="CR2" t="n">
-        <v>0.043449998</v>
-      </c>
       <c r="CS2" t="n">
-        <v>0.13241</v>
-      </c>
-      <c r="CT2" t="inlineStr">
+        <v>0.041840002</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="CU2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>002489.SZ</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
+      <c r="DA2" t="b">
         <v>0</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>-1.822915</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>3.77</v>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>YOTRIO GROUP CO LTD</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Yotrio Group Co., Ltd.</t>
+        </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>YOTRIO GROUP CO LTD</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>1780038258</v>
+      <c r="DF2" t="n">
+        <v>1782111876</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>SHZ</t>
+          <t>finmb_59263363</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>finmb_59263363</t>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DK2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DN2" t="b">
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
+      <c r="DN2" t="n">
+        <v>-3.2894704</v>
+      </c>
       <c r="DO2" t="n">
-        <v>0.6099999</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.19303794</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>3.16 - 4.21</t>
-        </is>
+        <v>2.94</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>15</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.44000006</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.10451308</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-1.566577</v>
+        <v>15</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
+        <v>1283995800000</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.099999905</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2.88 - 3.02</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>47347494</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.059999943</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.020833313</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>2.88 - 4.21</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.3016627</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-14.606744</v>
+      </c>
+      <c r="EF2" t="n">
         <v>1651229940</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EG2" t="n">
         <v>1651492800</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EH2" t="n">
         <v>0.11</v>
       </c>
-      <c r="DX2" t="n">
-        <v>0.23379993</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.066116154</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.043299913</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.011618835</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Yotrio Group Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1283995800000</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.06999993</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>3.75 - 3.93</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
+      <c r="EI2" t="n">
+        <v>-0.62520003</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.17536184</v>
       </c>
       <c r="EK2" t="n">
-        <v>42146043</v>
-      </c>
-      <c r="EL2" t="inlineStr"/>
+        <v>-0.7641499</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.20629562</v>
+      </c>
+      <c r="EM2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
